--- a/public/stays-import-template.xlsx
+++ b/public/stays-import-template.xlsx
@@ -670,8 +670,8 @@
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="縣市不正確" error="請從下拉選單選擇，用短名（宜蘭，不是宜蘭縣）" type="list">
       <formula1>"台北,新北,基隆,桃園,新竹市,新竹縣,苗栗,台中,彰化,南投,雲林,嘉義市,嘉義縣,台南,高雄,屏東,宜蘭,花蓮,台東,澎湖,金門,連江"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="風格不正確" error="請從下拉選單選擇六選一" type="list">
-      <formula1>"海景度假,山林小屋,設計旅宿,親子友善,寵物友善,包棟民宿"</formula1>
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="風格不正確" error="請從下拉選單選擇" type="list">
+      <formula1>"海景度假,山林小屋,設計旅宿,親子友善,寵物友善,包棟民宿,復古老宅"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="可住人數不正確" error="請填 1~100 的整數" type="whole" operator="between">
       <formula1>1</formula1>
@@ -784,7 +784,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>只能填下拉選單的六選一，對應前台的風格篩選。</t>
+          <t>只能填下拉選單裡的值，對應前台的風格篩選。</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• 風格可填值：海景度假、山林小屋、設計旅宿、親子友善、寵物友善、包棟民宿</t>
+          <t>• 風格可填值：海景度假、山林小屋、設計旅宿、親子友善、寵物友善、包棟民宿、復古老宅</t>
         </is>
       </c>
     </row>
